--- a/2026/SAENZ PEÑA/Abril/SAENZ_EXPENSAS-Abril.xlsx
+++ b/2026/SAENZ PEÑA/Abril/SAENZ_EXPENSAS-Abril.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SAENZ PEÑA\Abril\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SAENZ PEÑA\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2978B2-D862-42FC-81DD-FA627540DF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C040CD6A-3A12-4203-AA96-0422C16D5318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -19,14 +19,19 @@
     <sheet name="extraordinaria" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="76">
   <si>
     <t>UF</t>
   </si>
@@ -232,9 +237,6 @@
     <t>Prevision</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
     <t>PRESUPUESTO APROBADO - MANO DE OBRA GAS Y CLOACAS</t>
   </si>
   <si>
@@ -247,16 +249,16 @@
     <t xml:space="preserve">  </t>
   </si>
   <si>
-    <t xml:space="preserve">ADMA - Contactor modular Bipolar </t>
-  </si>
-  <si>
-    <t>Destapacion - Forlini Nora</t>
-  </si>
-  <si>
     <t>Liquidacion mes de ABRIL</t>
   </si>
   <si>
     <t xml:space="preserve">Período ABRIL </t>
+  </si>
+  <si>
+    <t>Destapacion - 22/04 Destapacion de cañeria cloacal desde camara hacia onodor en dpto B y desde camara hacia pozo. Se extrajo papel higenico - Dia 25/04: Destapacio de inodoro en dpto B - Se extrajo un trapo</t>
+  </si>
+  <si>
+    <t>Desagote de Pozo - Camiones Villar</t>
   </si>
 </sst>
 </file>
@@ -271,7 +273,7 @@
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_ &quot;$&quot;\ * #,##0.0_ ;_ &quot;$&quot;\ * \-#,##0.0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -379,13 +381,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1350,8 +1345,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1430,9 +1429,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1470,9 +1469,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1505,9 +1504,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1540,9 +1556,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1719,23 +1752,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H64"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>20</v>
       </c>
@@ -1743,29 +1776,29 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D6" s="28"/>
       <c r="E6" s="28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
@@ -1773,11 +1806,11 @@
       <c r="C7" s="59"/>
       <c r="D7" s="59"/>
       <c r="E7" s="24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F7" s="98"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1785,12 +1818,12 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="101" t="s">
         <v>12</v>
       </c>
@@ -1802,7 +1835,7 @@
       </c>
       <c r="F11" s="128"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="99"/>
       <c r="B12" s="99"/>
       <c r="C12" s="105"/>
@@ -1811,17 +1844,17 @@
         <v>48</v>
       </c>
       <c r="F12" s="121">
-        <v>1870625.3392361405</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1810783.8092361402</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="97" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="97" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="148">
+      <c r="C13" s="105">
         <v>40499</v>
       </c>
       <c r="D13" s="36"/>
@@ -1830,17 +1863,17 @@
       </c>
       <c r="F13" s="50">
         <f>'prorrateo '!F11</f>
-        <v>312200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>467450.20456200006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="99" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="148">
+      <c r="C14" s="105">
         <v>38128.82</v>
       </c>
       <c r="D14" s="5"/>
@@ -1848,11 +1881,11 @@
         <v>22</v>
       </c>
       <c r="F14" s="50">
-        <f>-(C37)</f>
-        <v>-370820.30000000005</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <f>-(C36)</f>
+        <v>-642995.82000000007</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="97" t="s">
         <v>21</v>
       </c>
@@ -1866,22 +1899,22 @@
       <c r="E15" s="49"/>
       <c r="F15" s="50"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="99" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B16" s="97"/>
-      <c r="C16" s="149">
+      <c r="C16" s="71">
         <v>10568</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="49"/>
       <c r="F16" s="50"/>
       <c r="H16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="102"/>
       <c r="B17" s="103"/>
       <c r="C17" s="125">
@@ -1893,10 +1926,10 @@
       </c>
       <c r="F17" s="118">
         <f>SUM(F12:F15)</f>
-        <v>1812005.0392361402</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1635238.1937981404</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="101" t="s">
         <v>23</v>
       </c>
@@ -1906,249 +1939,238 @@
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="97" t="s">
         <v>42</v>
       </c>
       <c r="B19" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="149">
+        <v>73</v>
+      </c>
+      <c r="C19" s="71">
         <v>88800</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="97" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="104"/>
+    <row r="20" spans="1:7" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="148" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="149"/>
       <c r="C20" s="71">
-        <v>37824.480000000003</v>
+        <v>210000</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="97" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B21" s="104"/>
-      <c r="C21" s="71">
-        <v>120000</v>
+      <c r="C21" s="105">
+        <v>220000</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="97" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B22" s="104"/>
-      <c r="C22" s="105">
-        <v>0</v>
-      </c>
+      <c r="C22" s="105"/>
       <c r="D22" s="5"/>
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="97" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="104"/>
-      <c r="C23" s="105"/>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="102"/>
+      <c r="B23" s="103"/>
+      <c r="C23" s="119">
+        <f>SUM(C18:C22)</f>
+        <v>518800</v>
+      </c>
       <c r="D23" s="5"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="102"/>
-      <c r="B24" s="103"/>
-      <c r="C24" s="119">
-        <f>SUM(C18:C23)</f>
-        <v>246624.48</v>
+      <c r="E23" s="5"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="41"/>
+      <c r="C24" s="120">
+        <f>+C23+C17</f>
+        <v>642995.82000000007</v>
       </c>
       <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="41"/>
-      <c r="C25" s="120">
-        <f>+C24+C17</f>
-        <v>370820.30000000005</v>
-      </c>
-      <c r="D25" s="5"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="20"/>
+    </row>
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="73"/>
+      <c r="C25" s="74"/>
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="60" t="s">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="73"/>
-      <c r="C26" s="74"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="20"/>
-    </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="46"/>
+    </row>
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="37"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="46"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="44"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="45">
+        <v>0</v>
+      </c>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="44"/>
-      <c r="B29" s="43"/>
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="52"/>
+      <c r="B29" s="53"/>
       <c r="C29" s="45">
         <v>0</v>
       </c>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="52"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="45">
-        <v>0</v>
-      </c>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="69"/>
+      <c r="B30" s="70"/>
+      <c r="C30" s="72"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="69"/>
-      <c r="B31" s="70"/>
-      <c r="C31" s="72"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="77"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="69"/>
-      <c r="B32" s="76"/>
-      <c r="C32" s="77"/>
+      <c r="B32" s="75"/>
+      <c r="C32" s="72">
+        <v>0</v>
+      </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="69"/>
-      <c r="B33" s="75"/>
-      <c r="C33" s="72">
-        <v>0</v>
-      </c>
-      <c r="F33" s="6"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="54" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="55"/>
-      <c r="C34" s="56">
-        <f>SUM(C29:C33)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="B33" s="55"/>
+      <c r="C33" s="56">
+        <f>SUM(C28:C32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="122">
-        <f>C25-C23</f>
-        <v>370820.30000000005</v>
-      </c>
+      <c r="C34" s="122">
+        <f>C24-C22</f>
+        <v>642995.82000000007</v>
+      </c>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="123">
+        <f>+C24</f>
+        <v>642995.82000000007</v>
+      </c>
+      <c r="E35" s="100"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C36" s="123">
-        <f>+C25</f>
-        <v>370820.30000000005</v>
-      </c>
-      <c r="E36" s="100"/>
-      <c r="F36" s="6"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="54" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="55"/>
-      <c r="C37" s="124">
-        <f>C35</f>
-        <v>370820.30000000005</v>
-      </c>
-      <c r="E37" s="16"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="55"/>
+      <c r="C36" s="124">
+        <f>C34</f>
+        <v>642995.82000000007</v>
+      </c>
+      <c r="E36" s="16"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D43" s="16"/>
       <c r="E43" s="16"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D45" s="16"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D46" s="16"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="19"/>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="19"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="20"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="18"/>
       <c r="B58" s="18"/>
-      <c r="C58" s="20"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C58" s="18"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="18"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="18"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A20:B20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2166,24 +2188,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="95" t="s">
         <v>60</v>
       </c>
@@ -2205,7 +2227,7 @@
       </c>
       <c r="L1" s="27"/>
     </row>
-    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="63" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de ABRIL</v>
@@ -2224,7 +2246,7 @@
       <c r="K2" s="67"/>
       <c r="L2" s="68"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2262,7 +2284,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2292,7 +2314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2306,18 +2328,16 @@
         <v>0.1512</v>
       </c>
       <c r="E5" s="34">
-        <v>649812.63754278515</v>
-      </c>
-      <c r="F5" s="127">
-        <v>100000</v>
-      </c>
+        <v>652249.57843237906</v>
+      </c>
+      <c r="F5" s="127"/>
       <c r="G5" s="58">
         <f>E5-F5</f>
-        <v>549812.63754278515</v>
+        <v>652249.57843237906</v>
       </c>
       <c r="H5" s="61">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
-        <v>46184.261553593955</v>
+        <v>54788.964588319846</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
@@ -2332,10 +2352,10 @@
       </c>
       <c r="L5" s="32">
         <f>J5+K5+H5+G5</f>
-        <v>652249.57843237906</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>763291.22235669894</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2349,15 +2369,15 @@
         <v>0.15690000000000001</v>
       </c>
       <c r="E6" s="34">
-        <v>39225</v>
+        <v>58373.316057000011</v>
       </c>
       <c r="F6" s="127">
-        <f>E6</f>
-        <v>39225</v>
+        <f>'detalle y gastos'!C20</f>
+        <v>210000</v>
       </c>
       <c r="G6" s="58">
         <f t="shared" ref="G6:G8" si="0">E6-F6</f>
-        <v>0</v>
+        <v>-151626.68394299998</v>
       </c>
       <c r="H6" s="61">
         <f t="shared" ref="H6:H10" si="1">IF(G6&gt;0,G6*8.4%,0)</f>
@@ -2376,10 +2396,10 @@
       </c>
       <c r="L6" s="32">
         <f>J6+K6+H6+G6</f>
-        <v>58373.316057000011</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>-93253.367885999964</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2393,11 +2413,11 @@
         <v>0.15820000000000001</v>
       </c>
       <c r="E7" s="34">
-        <v>39550</v>
+        <v>58856.970046000009</v>
       </c>
       <c r="F7" s="127">
         <f>E7</f>
-        <v>39550</v>
+        <v>58856.970046000009</v>
       </c>
       <c r="G7" s="58">
         <f t="shared" si="0"/>
@@ -2423,7 +2443,7 @@
         <v>58856.970046000009</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2437,11 +2457,11 @@
         <v>0.19800000000000001</v>
       </c>
       <c r="E8" s="34">
-        <v>49500</v>
+        <v>73664.222940000007</v>
       </c>
       <c r="F8" s="127">
         <f>E8</f>
-        <v>49500</v>
+        <v>73664.222940000007</v>
       </c>
       <c r="G8" s="58">
         <f t="shared" si="0"/>
@@ -2467,7 +2487,7 @@
         <v>73664.222940000007</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2481,11 +2501,11 @@
         <v>0.15920000000000001</v>
       </c>
       <c r="E9" s="34">
-        <v>39800</v>
+        <v>59229.011576000004</v>
       </c>
       <c r="F9" s="127">
         <f>E9</f>
-        <v>39800</v>
+        <v>59229.011576000004</v>
       </c>
       <c r="G9" s="58">
         <f>E9-F9</f>
@@ -2511,7 +2531,7 @@
         <v>59229.011576000004</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -2525,15 +2545,14 @@
         <v>0.17649999999999999</v>
       </c>
       <c r="E10" s="34">
-        <v>44125</v>
+        <v>65665.330044999995</v>
       </c>
       <c r="F10" s="127">
-        <f>E10</f>
-        <v>44125</v>
+        <v>65700</v>
       </c>
       <c r="G10" s="58">
         <f>E10-F10</f>
-        <v>0</v>
+        <v>-34.669955000004848</v>
       </c>
       <c r="H10" s="61">
         <f t="shared" si="1"/>
@@ -2552,10 +2571,10 @@
       </c>
       <c r="L10" s="32">
         <f>J10+K10+H10+G10</f>
-        <v>65665.330044999995</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>65630.66008999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
@@ -2567,19 +2586,19 @@
       </c>
       <c r="E11" s="35">
         <f t="shared" ref="E11" si="3">SUM(E5:E10)</f>
-        <v>862012.63754278515</v>
+        <v>968038.42909637897</v>
       </c>
       <c r="F11" s="35">
         <f>SUM(F5:F10)</f>
-        <v>312200</v>
+        <v>467450.20456200006</v>
       </c>
       <c r="G11" s="42">
         <f>SUM(G5:G10)</f>
-        <v>549812.63754278515</v>
+        <v>500588.22453437909</v>
       </c>
       <c r="H11" s="42">
         <f t="shared" ref="H11:K11" si="4">SUM(H5:H10)</f>
-        <v>46184.261553593955</v>
+        <v>54788.964588319846</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="4"/>
@@ -2595,10 +2614,10 @@
       </c>
       <c r="L11" s="42">
         <f>SUM(L5:L10)</f>
-        <v>968038.42909637897</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>927418.719122699</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="129"/>
       <c r="B12" s="129"/>
       <c r="C12" s="129"/>
@@ -2612,10 +2631,10 @@
       <c r="K12" s="129"/>
       <c r="L12" s="129"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L13" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
@@ -2635,23 +2654,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="106" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="107"/>
       <c r="C1" s="107"/>
@@ -2664,7 +2683,7 @@
       <c r="H1" s="130"/>
       <c r="I1" s="110"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -2693,7 +2712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2714,7 +2733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>1</v>
       </c>
@@ -2746,7 +2765,7 @@
         <v>680400</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>2</v>
       </c>
@@ -2778,7 +2797,7 @@
         <v>706050</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>3</v>
       </c>
@@ -2810,7 +2829,7 @@
         <v>711900</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>4</v>
       </c>
@@ -2842,7 +2861,7 @@
         <v>891000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>5</v>
       </c>
@@ -2874,7 +2893,7 @@
         <v>716400</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>6</v>
       </c>
@@ -2906,7 +2925,7 @@
         <v>794250</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="113" t="s">
         <v>10</v>
       </c>
@@ -2937,7 +2956,7 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="129"/>
       <c r="B11" s="129"/>
       <c r="C11" s="129"/>
@@ -2948,10 +2967,10 @@
       <c r="H11" s="129"/>
       <c r="I11" s="129"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I12" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>
@@ -2969,12 +2988,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="136" t="s">
         <v>27</v>
       </c>
@@ -2985,7 +3004,7 @@
       <c r="F1" s="78"/>
       <c r="G1" s="78"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="139" t="s">
         <v>55</v>
       </c>
@@ -2998,7 +3017,7 @@
       <c r="F2" s="79"/>
       <c r="G2" s="79"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="144" t="s">
         <v>0</v>
       </c>
@@ -3021,7 +3040,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="145"/>
       <c r="B4" s="145"/>
       <c r="C4" s="145"/>
@@ -3030,7 +3049,7 @@
       <c r="F4" s="132"/>
       <c r="G4" s="132"/>
     </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="80">
         <v>1</v>
       </c>
@@ -3053,7 +3072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="80">
         <v>2</v>
       </c>
@@ -3076,7 +3095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="80">
         <v>3</v>
       </c>
@@ -3099,7 +3118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="80">
         <v>4</v>
       </c>
@@ -3122,7 +3141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="80">
         <v>5</v>
       </c>
@@ -3145,7 +3164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="85">
         <v>6</v>
       </c>
@@ -3168,7 +3187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="90" t="s">
         <v>10</v>
       </c>
@@ -3187,7 +3206,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="133"/>
       <c r="B12" s="134"/>
       <c r="C12" s="134"/>
